--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D42214B-CD98-4D9D-85F4-0A42E35A8B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7530" tabRatio="916" activeTab="5"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -29,17 +30,28 @@
     <sheet name="Web" sheetId="16" r:id="rId15"/>
     <sheet name="大模型相关" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="176">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -652,13 +664,17 @@
   </si>
   <si>
     <t>20260204-Python-装饰器的灵活实现：带参数与不带参数.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1017,16 +1033,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="2" max="2" width="42.77734375" customWidth="1"/>
-    <col min="3" max="3" width="92.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.3046875" customWidth="1"/>
+    <col min="2" max="2" width="42.765625" customWidth="1"/>
+    <col min="3" max="3" width="92.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1037,7 +1053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1049,7 +1065,7 @@
         <v>- [Python_polars学习-01_读取与写入文件](polars-学习/Python_polars学习-01_读取与写入文件.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1061,7 +1077,7 @@
         <v>- [Python_polars学习-02_上下文与表达式](polars-学习/Python_polars学习-02_上下文与表达式.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1089,7 @@
         <v>- [Python_polars学习-03_数据类型转换](polars-学习/Python_polars学习-03_数据类型转换.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1085,7 +1101,7 @@
         <v>- [Python_polars学习-04_字符串数据处理](polars-学习/Python_polars学习-04_字符串数据处理.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1097,7 +1113,7 @@
         <v>- [Python_polars学习-05_包含的数据结构](polars-学习/Python_polars学习-05_包含的数据结构.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1109,7 +1125,7 @@
         <v>- [Python_polars学习-06_Lazy-Eager-API](polars-学习/Python_polars学习-06_Lazy-Eager-API.md)</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1137,7 @@
         <v>- [Python_polars学习-07_缺失值](polars-学习/Python_polars学习-07_缺失值.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1149,7 @@
         <v>- [Python_polars学习-08_分类数据处理](polars-学习/Python_polars学习-08_分类数据处理.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1145,7 +1161,7 @@
         <v>- [Python_polars学习-09_数据框关联与拼接](polars-学习/Python_polars学习-09_数据框关联与拼接.md)</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1173,7 @@
         <v>- [Python-polars学习-10-时间序列类型](polars-学习/Python-polars学习-10-时间序列类型.md)</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1185,7 @@
         <v>- [Python-polars学习-11-用户自定义函数](polars-学习/Python-polars学习-11-用户自定义函数.md)</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1178,7 +1194,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1187,7 +1203,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1203,17 +1219,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.21875" customWidth="1"/>
-    <col min="4" max="4" width="106.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="35.23046875" customWidth="1"/>
+    <col min="4" max="4" width="106.23046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1227,7 +1243,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1243,7 +1259,7 @@
         <v>- [《精益数据分析》读书分享-----增长引擎说](/数据分析与挖掘/《精益数据分析》读书分享-----增长引擎说.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1259,7 +1275,7 @@
         <v>- [不同岗位的数据分析人员，可能使用不同的分析方法](/数据分析与挖掘/不同岗位的数据分析人员，可能使用不同的分析方法.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -1275,7 +1291,7 @@
         <v>- [传统统计分析在Python中的使用](/数据分析与挖掘/传统统计分析在Python中的使用.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -1291,7 +1307,7 @@
         <v>- [机器学习-决策树原理-Python](/数据分析与挖掘/机器学习-决策树原理-Python.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -1303,7 +1319,7 @@
         <v>- [机器学习算法总结](数据分析与挖掘/机器学习算法总结.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>89</v>
       </c>
@@ -1315,7 +1331,7 @@
         <v>- [机器学习之sklearn-feature_selection-chi2基于卡方，特征筛选详解](数据分析与挖掘/机器学习之sklearn-feature_selection-chi2基于卡方，特征筛选详解.md)</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -1327,7 +1343,7 @@
         <v>- [利用熵值法确定指标权重---原理及Python实现](数据分析与挖掘/利用熵值法确定指标权重---原理及Python实现.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -1339,7 +1355,7 @@
         <v>- [Python-利用数据分布直方图来确定合适的阈值](数据分析与挖掘/Python-利用数据分布直方图来确定合适的阈值.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>89</v>
       </c>
@@ -1351,7 +1367,7 @@
         <v>- [Python-如何确定K-Means聚类的簇数](数据分析与挖掘/Python-如何确定K-Means聚类的簇数.md)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -1360,7 +1376,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1369,7 +1385,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -1378,7 +1394,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -1387,7 +1403,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1396,7 +1412,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>89</v>
       </c>
@@ -1405,7 +1421,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -1414,7 +1430,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -1423,7 +1439,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -1432,7 +1448,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -1441,7 +1457,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -1450,7 +1466,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>89</v>
       </c>
@@ -1459,7 +1475,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -1468,7 +1484,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -1477,7 +1493,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -1486,7 +1502,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -1495,7 +1511,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -1504,7 +1520,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -1513,7 +1529,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>89</v>
       </c>
@@ -1522,7 +1538,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>89</v>
       </c>
@@ -1531,7 +1547,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>89</v>
       </c>
@@ -1540,7 +1556,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>89</v>
       </c>
@@ -1549,7 +1565,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -1558,7 +1574,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>89</v>
       </c>
@@ -1567,7 +1583,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>89</v>
       </c>
@@ -1576,7 +1592,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>89</v>
       </c>
@@ -1585,7 +1601,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -1594,7 +1610,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -1603,7 +1619,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -1612,7 +1628,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1621,7 +1637,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>89</v>
       </c>
@@ -1637,17 +1653,17 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" customWidth="1"/>
-    <col min="4" max="4" width="57.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="36.69140625" customWidth="1"/>
+    <col min="4" max="4" width="57.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1661,7 +1677,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -1677,7 +1693,7 @@
         <v>- [利用Python+PyEcharts画出《人民日报》各国疫情图](/数据可视化/利用Python+PyEcharts画出《人民日报》各国疫情图.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -1693,7 +1709,7 @@
         <v>- [利用Python画出《人民日报》各国疫情图——南丁格尔玫瑰图](/数据可视化/利用Python画出《人民日报》各国疫情图——南丁格尔玫瑰图.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>99</v>
       </c>
@@ -1709,7 +1725,7 @@
         <v>- [罗兰贝格图--Python等高线图（平滑处理）](/数据可视化/罗兰贝格图--Python等高线图（平滑处理）.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -1725,7 +1741,7 @@
         <v>- [Matplotlib-自定义函数实现左边柱形图，右边饼图](/数据可视化/Matplotlib-自定义函数实现左边柱形图，右边饼图.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>99</v>
       </c>
@@ -1741,7 +1757,7 @@
         <v>- [Python-基于pyecharts自定义经纬度热力图可视化](/数据可视化/Python-基于pyecharts自定义经纬度热力图可视化.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -1757,7 +1773,7 @@
         <v>- [Python-利用Matplotlib制作初中时圆规画的图](/数据可视化/Python-利用Matplotlib制作初中时圆规画的图.md)</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -1773,7 +1789,7 @@
         <v>- [Python-基于Matplotlib制作动态图](/数据可视化/Python-基于Matplotlib制作动态图.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>99</v>
       </c>
@@ -1789,7 +1805,7 @@
         <v>- [Python-基于plotly库快速画旭日图](/数据可视化/Python-基于plotly库快速画旭日图.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -1805,7 +1821,7 @@
         <v>- [Python-基于plotly库快速绘制时间线图](/数据可视化/Python-基于plotly库快速绘制时间线图.md)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>99</v>
       </c>
@@ -1818,7 +1834,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>99</v>
       </c>
@@ -1831,7 +1847,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -1844,7 +1860,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -1857,7 +1873,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -1870,7 +1886,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>99</v>
       </c>
@@ -1883,7 +1899,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1896,7 +1912,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -1909,7 +1925,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -1922,7 +1938,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -1935,7 +1951,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -1948,7 +1964,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -1961,7 +1977,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -1974,7 +1990,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -1987,7 +2003,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>99</v>
       </c>
@@ -2000,7 +2016,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>99</v>
       </c>
@@ -2013,7 +2029,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>99</v>
       </c>
@@ -2026,7 +2042,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>99</v>
       </c>
@@ -2039,7 +2055,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -2052,7 +2068,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>99</v>
       </c>
@@ -2065,7 +2081,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -2078,7 +2094,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -2091,7 +2107,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>99</v>
       </c>
@@ -2104,7 +2120,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -2117,7 +2133,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -2130,7 +2146,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>99</v>
       </c>
@@ -2143,7 +2159,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -2156,7 +2172,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>99</v>
       </c>
@@ -2169,7 +2185,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>99</v>
       </c>
@@ -2182,7 +2198,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -2195,7 +2211,7 @@
         <v>- [](/数据可视化/)</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>99</v>
       </c>
@@ -2215,17 +2231,17 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="36.77734375" customWidth="1"/>
-    <col min="4" max="4" width="79.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="36.765625" customWidth="1"/>
+    <col min="4" max="4" width="79.765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2239,7 +2255,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -2255,7 +2271,7 @@
         <v>- [分类问题中Sigmoid-与-Softmax-区别](/数学知识/分类问题中Sigmoid-与-Softmax-区别.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>107</v>
       </c>
@@ -2271,7 +2287,7 @@
         <v>- [利用Python枚举所有的排列情况](/数学知识/利用Python枚举所有的排列情况.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>107</v>
       </c>
@@ -2287,7 +2303,7 @@
         <v>- [让ChatGPT回答闰年的计算逻辑](/数学知识/让ChatGPT回答闰年的计算逻辑.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -2303,7 +2319,7 @@
         <v>- [Python-使用sklearn计算余弦相似度](/数学知识/Python-使用sklearn计算余弦相似度.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -2319,7 +2335,7 @@
         <v>- [Python利用枚举法，解决一道面试算法题](/数学知识/Python利用枚举法，解决一道面试算法题.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -2332,7 +2348,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>107</v>
       </c>
@@ -2345,7 +2361,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -2358,7 +2374,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>107</v>
       </c>
@@ -2371,7 +2387,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -2384,7 +2400,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>107</v>
       </c>
@@ -2397,7 +2413,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>107</v>
       </c>
@@ -2410,7 +2426,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>107</v>
       </c>
@@ -2423,7 +2439,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -2436,7 +2452,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>107</v>
       </c>
@@ -2449,7 +2465,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>107</v>
       </c>
@@ -2462,7 +2478,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>107</v>
       </c>
@@ -2475,7 +2491,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>107</v>
       </c>
@@ -2488,7 +2504,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>107</v>
       </c>
@@ -2501,7 +2517,7 @@
         <v>- [](/数学知识/)</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>107</v>
       </c>
@@ -2510,7 +2526,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -2519,7 +2535,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>107</v>
       </c>
@@ -2528,7 +2544,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>107</v>
       </c>
@@ -2537,7 +2553,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>107</v>
       </c>
@@ -2546,7 +2562,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -2555,7 +2571,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -2564,7 +2580,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -2573,7 +2589,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>107</v>
       </c>
@@ -2582,7 +2598,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -2591,7 +2607,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>107</v>
       </c>
@@ -2600,7 +2616,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>107</v>
       </c>
@@ -2609,7 +2625,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -2618,7 +2634,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -2627,7 +2643,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -2636,7 +2652,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -2645,7 +2661,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>107</v>
       </c>
@@ -2654,7 +2670,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>107</v>
       </c>
@@ -2663,7 +2679,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>107</v>
       </c>
@@ -2672,7 +2688,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>107</v>
       </c>
@@ -2681,7 +2697,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>107</v>
       </c>
@@ -2697,17 +2713,17 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
-    <col min="4" max="4" width="91.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="24.4609375" customWidth="1"/>
+    <col min="4" max="4" width="91.23046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2721,7 +2737,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -2737,7 +2753,7 @@
         <v>- [工欲善其事必先利其器](/随笔/工欲善其事必先利其器.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -2753,7 +2769,7 @@
         <v>- [吴军老师的《计算之魂》部分重点摘要](/随笔/吴军老师的《计算之魂》部分重点摘要.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -2766,7 +2782,7 @@
         <v>- [](/随笔/)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -2782,7 +2798,7 @@
         <v>- [从互联网+，到DeepSeek+，新一轮的技术变革](/随笔/从互联网+，到DeepSeek+，新一轮的技术变革.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -2798,7 +2814,7 @@
         <v>- [管理的精髓](/随笔/管理的精髓.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -2807,7 +2823,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -2816,7 +2832,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -2825,7 +2841,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -2834,7 +2850,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -2843,7 +2859,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -2852,7 +2868,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -2861,7 +2877,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -2870,7 +2886,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -2879,7 +2895,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -2888,7 +2904,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -2897,7 +2913,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>113</v>
       </c>
@@ -2906,7 +2922,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -2915,7 +2931,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -2924,7 +2940,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>113</v>
       </c>
@@ -2933,7 +2949,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -2942,7 +2958,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -2951,7 +2967,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -2960,7 +2976,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -2969,7 +2985,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -2978,7 +2994,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>113</v>
       </c>
@@ -2987,7 +3003,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>113</v>
       </c>
@@ -2996,7 +3012,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>113</v>
       </c>
@@ -3005,7 +3021,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>113</v>
       </c>
@@ -3014,7 +3030,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -3023,7 +3039,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -3032,7 +3048,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -3041,7 +3057,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>113</v>
       </c>
@@ -3050,7 +3066,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>113</v>
       </c>
@@ -3059,7 +3075,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -3068,7 +3084,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>113</v>
       </c>
@@ -3077,7 +3093,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -3086,7 +3102,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -3095,7 +3111,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>113</v>
       </c>
@@ -3104,7 +3120,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -3120,16 +3136,16 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="2" max="2" width="42.6640625" customWidth="1"/>
-    <col min="3" max="3" width="74.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.765625" customWidth="1"/>
+    <col min="2" max="2" width="42.69140625" customWidth="1"/>
+    <col min="3" max="3" width="74.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3140,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -3152,7 +3168,7 @@
         <v>- [Clickhouse-读取存储在hdfs的hive表数据](Clickhouse/Clickhouse-读取存储在hdfs的hive表数据.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -3164,7 +3180,7 @@
         <v>- [Clickhouse-基础使用教程](Clickhouse/Clickhouse-基础使用教程.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -3176,7 +3192,7 @@
         <v>- [Clickhouse中创建生成日期序列自定义函数](Clickhouse/Clickhouse中创建生成日期序列自定义函数.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -3185,7 +3201,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>126</v>
       </c>
@@ -3194,7 +3210,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>126</v>
       </c>
@@ -3203,7 +3219,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -3212,7 +3228,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>126</v>
       </c>
@@ -3221,7 +3237,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>126</v>
       </c>
@@ -3230,7 +3246,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -3239,7 +3255,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -3248,7 +3264,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -3257,7 +3273,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -3266,7 +3282,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>126</v>
       </c>
@@ -3275,7 +3291,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>126</v>
       </c>
@@ -3284,7 +3300,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>126</v>
       </c>
@@ -3293,7 +3309,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -3302,7 +3318,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -3311,7 +3327,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>126</v>
       </c>
@@ -3320,7 +3336,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -3329,7 +3345,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -3338,7 +3354,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -3347,7 +3363,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>126</v>
       </c>
@@ -3356,7 +3372,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>126</v>
       </c>
@@ -3372,17 +3388,17 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.23046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="93.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3396,7 +3412,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -3412,7 +3428,7 @@
         <v>- [Python中一个构建-web-页面的神奇库-streamlit](/Web/Python中一个构建-web-页面的神奇库-streamlit.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>146</v>
       </c>
@@ -3425,7 +3441,7 @@
         <v>- [](/Web/)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -3438,7 +3454,7 @@
         <v>- [](/Web/)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -3451,7 +3467,7 @@
         <v>- [](/Web/)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -3464,7 +3480,7 @@
         <v>- [](/Web/)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -3473,7 +3489,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>146</v>
       </c>
@@ -3482,7 +3498,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -3491,7 +3507,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>146</v>
       </c>
@@ -3500,7 +3516,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>146</v>
       </c>
@@ -3509,7 +3525,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -3518,7 +3534,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -3527,7 +3543,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>146</v>
       </c>
@@ -3536,7 +3552,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>146</v>
       </c>
@@ -3545,7 +3561,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>146</v>
       </c>
@@ -3561,16 +3577,16 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="44.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.69140625" customWidth="1"/>
+    <col min="2" max="2" width="44.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3581,7 +3597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -3593,7 +3609,7 @@
         <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -3602,7 +3618,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -3611,7 +3627,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -3620,7 +3636,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>152</v>
       </c>
@@ -3629,7 +3645,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>152</v>
       </c>
@@ -3638,7 +3654,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -3647,7 +3663,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>152</v>
       </c>
@@ -3656,7 +3672,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -3665,7 +3681,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -3674,7 +3690,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>152</v>
       </c>
@@ -3683,7 +3699,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -3692,7 +3708,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>152</v>
       </c>
@@ -3701,7 +3717,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -3710,7 +3726,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>152</v>
       </c>
@@ -3726,17 +3742,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="40.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.3046875" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="40.84375" customWidth="1"/>
     <col min="4" max="4" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3750,7 +3766,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -3766,7 +3782,7 @@
         <v>- [Hive---HQL支持的2种查询语句风格，你喜欢哪一种？](/Hive/Hive---HQL支持的2种查询语句风格，你喜欢哪一种？.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3782,7 +3798,7 @@
         <v>- [Hive-数据聚合成键值对时，根据值大小进行排序](/Hive/Hive-数据聚合成键值对时，根据值大小进行排序.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3798,7 +3814,7 @@
         <v>- [Hive-中把一行记录拆分为多行记录](/Hive/Hive-中把一行记录拆分为多行记录.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3814,7 +3830,7 @@
         <v>- [Hive中的常用函数](/Hive/Hive中的常用函数.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3830,7 +3846,7 @@
         <v>- [Hive-中的各种常用set设置](/Hive/Hive-中的各种常用set设置.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3845,7 +3861,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3861,7 +3877,7 @@
         <v>- [Hive中各种日期格式转换方法总结](/Hive/Hive中各种日期格式转换方法总结.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3877,7 +3893,7 @@
         <v>- [hadoop-常用命令总结](/Hive/hadoop-常用命令总结.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3886,7 +3902,7 @@
         <v>- [](/Hive/)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3895,7 +3911,7 @@
         <v>- [](/Hive/)</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3904,7 +3920,7 @@
         <v>- [](/Hive/)</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -3912,7 +3928,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -3921,7 +3937,7 @@
         <v>- [](/Hive/)</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -3937,16 +3953,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.84375" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="24.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3957,7 +3973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3969,7 +3985,7 @@
         <v>- [Excel中的标准差stdev-S和stdev-P区别](EXCEL数据处理-VBA/Excel中的标准差stdev-S和stdev-P区别.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3981,7 +3997,7 @@
         <v>- [数据去重-----VBA字典法](EXCEL数据处理-VBA/数据去重-----VBA字典法.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3990,7 +4006,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3999,7 +4015,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -4008,7 +4024,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4017,7 +4033,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -4026,7 +4042,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -4035,32 +4051,32 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -4072,16 +4088,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.84375" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="24.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4092,7 +4108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4104,7 +4120,7 @@
         <v>- [Linux-（Centos-7）中-Anaconda环境管理，安装不同的版本Python包](Linux/Linux-（Centos-7）中-Anaconda环境管理，安装不同的版本Python包.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -4116,7 +4132,7 @@
         <v>- [Linux之NTFS、FAT32、exFAT-各种格式硬盘挂载整理](Linux/Linux之NTFS、FAT32、exFAT-各种格式硬盘挂载整理.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4128,7 +4144,7 @@
         <v>- [SecureCRT利用Python脚本自动登陆服务器，自动验证Google-Authenticator动态验证码](Linux/SecureCRT利用Python脚本自动登陆服务器，自动验证Google-Authenticator动态验证码.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -4140,7 +4156,7 @@
         <v>- [数据分析师常用的-Linux-命令总结](Linux/数据分析师常用的-Linux-命令总结.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4152,7 +4168,7 @@
         <v>- [在Linux服务器上部署Jupyter-notebook](Linux/在Linux服务器上部署Jupyter-notebook.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -4161,7 +4177,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4170,7 +4186,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -4179,32 +4195,32 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4216,17 +4232,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="24.4609375" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4240,7 +4256,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -4256,7 +4272,7 @@
         <v>- [Python-除了结巴分词，还有什么好用的中文分词工具？](/NLP/Python-除了结巴分词，还有什么好用的中文分词工具？.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4272,7 +4288,7 @@
         <v>- [Python调用apiKey试玩ChatGPT](/NLP/Python调用apiKey试玩ChatGPT.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -4288,7 +4304,7 @@
         <v>- [自然语言处理（NLP）-Bert与Lstm结合](/NLP/自然语言处理（NLP）-Bert与Lstm结合.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -4304,7 +4320,7 @@
         <v>- [基于DeepSeek，构建个人本地RAG知识库](/NLP/基于DeepSeek，构建个人本地RAG知识库.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -4317,7 +4333,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -4330,7 +4346,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4343,7 +4359,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -4356,7 +4372,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -4365,7 +4381,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -4374,7 +4390,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -4383,7 +4399,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -4392,7 +4408,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4401,7 +4417,7 @@
         <v>- [](/NLP/)</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -4417,17 +4433,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="58.5546875" customWidth="1"/>
-    <col min="3" max="3" width="88.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="58.53515625" customWidth="1"/>
+    <col min="3" max="3" width="88.53515625" customWidth="1"/>
+    <col min="4" max="4" width="23.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4441,7 +4457,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -4457,7 +4473,7 @@
         <v>- [NumPy论文都已经登上了Nature，Pythoneer会用了吗？](/Python基础库/NumPy论文都已经登上了Nature，Pythoneer会用了吗？.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -4473,7 +4489,7 @@
         <v>- [Python-标准库之pathlib，路径操作](/Python基础库/Python-标准库之pathlib，路径操作.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -4489,7 +4505,7 @@
         <v>- [Python-标准库heapq，堆数据结构操作详解](/Python基础库/Python-标准库heapq，堆数据结构操作详解.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -4505,7 +4521,7 @@
         <v>- [Python-基于ssh连接远程Mysql数据库](/Python基础库/Python-基于ssh连接远程Mysql数据库.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -4521,7 +4537,7 @@
         <v>- [Python-记录re正则模块，方便后期查找使用](/Python基础库/Python-记录re正则模块，方便后期查找使用.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -4537,7 +4553,7 @@
         <v>- [Python-内建模块-bisect，数组二分查找算法](/Python基础库/Python-内建模块-bisect，数组二分查找算法.md)</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -4553,7 +4569,7 @@
         <v>- [Python-扑克牌发牌游戏](/Python基础库/Python-扑克牌发牌游戏.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -4569,7 +4585,7 @@
         <v>- [Python-中一个好用的地址解析工具cpca（chinese_province_city_area_mapper）](/Python基础库/Python-中一个好用的地址解析工具cpca（chinese_province_city_area_mapper）.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -4585,7 +4601,7 @@
         <v>- [Python-字典已经是有序的，你知道吗？](/Python基础库/Python-字典已经是有序的，你知道吗？.md)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -4601,7 +4617,7 @@
         <v>- [Python-math模块详解](/Python基础库/Python-math模块详解.md)</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -4617,7 +4633,7 @@
         <v>- [Python利用partial偏函数，生成不同的聚合函数](/Python基础库/Python利用partial偏函数，生成不同的聚合函数.md)</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -4633,7 +4649,7 @@
         <v>- [Python内置的-os-模块常用函数、方法](/Python基础库/Python内置的-os-模块常用函数、方法.md)</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -4649,7 +4665,7 @@
         <v>- [Python文件打包成exe可执行程序](/Python基础库/Python文件打包成exe可执行程序.md)</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4662,7 +4678,7 @@
         <v>- [](/Python基础库/)</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -4678,7 +4694,7 @@
         <v>- [《Python-编程从新手到高手》知识点](/Python基础库/《Python-编程从新手到高手》知识点.md)</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -4694,7 +4710,7 @@
         <v>- [Python-单实例模式详解](/Python基础库/Python-单实例模式详解.md)</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4710,7 +4726,7 @@
         <v>- [Python函数参数：列表作为默认值，一个隐藏的陷阱！](/Python基础库/Python函数参数：列表作为默认值，一个隐藏的陷阱！.md)</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -4726,7 +4742,7 @@
         <v>- [Python-函数参数类型与使用规则详解](/Python基础库/Python-函数参数类型与使用规则详解.md)</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -4742,7 +4758,7 @@
         <v>- [Rust-是否会重写-Python-解释器与有关的库，替代-C-语言地位？](/Python基础库/Rust-是否会重写-Python-解释器与有关的库，替代-C-语言地位？.md)</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -4758,7 +4774,7 @@
         <v>- [Python-3-14-无GIL解释器性能测试：释放多核CPU的并行潜力](/Python基础库/Python-3-14-无GIL解释器性能测试：释放多核CPU的并行潜力.md)</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -4771,7 +4787,7 @@
         <v>- [](/Python基础库/)</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -4787,7 +4803,7 @@
         <v>- [Python-2个好用的装饰器函数](/Python基础库/Python-2个好用的装饰器函数.md)</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -4803,7 +4819,7 @@
         <v>- [Python-collections详解：解锁高效数据结构](/Python基础库/Python-collections详解：解锁高效数据结构.md)</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -4819,7 +4835,7 @@
         <v>- [Python-标准库之pathlib（二），路径操作](/Python基础库/Python-标准库之pathlib（二），路径操作.md)</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -4835,7 +4851,7 @@
         <v>- [Python-基于协程的端口扫描工具](/Python基础库/Python-基于协程的端口扫描工具.md)</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -4851,7 +4867,7 @@
         <v>- [Python-利用-uv-“一键”-快速部署服务](/Python基础库/Python-利用-uv-“一键”-快速部署服务.md)</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -4867,7 +4883,7 @@
         <v>- [Python-迈向强类型化的优雅转变](/Python基础库/Python-迈向强类型化的优雅转变.md)</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -4883,7 +4899,7 @@
         <v>- [Python-项目管理新思路：用-uv-Workspace-共享虚拟环境，省时省空间！](/Python基础库/Python-项目管理新思路：用-uv-Workspace-共享虚拟环境，省时省空间！.md)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -4899,7 +4915,7 @@
         <v>- [Python-新晋包项目工具uv的简单尝试](/Python基础库/Python-新晋包项目工具uv的简单尝试.md)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -4915,12 +4931,12 @@
         <v>- [Python-在指定文件夹安装三方库，并进行加载使用](/Python基础库/Python-在指定文件夹安装三方库，并进行加载使用.md)</v>
       </c>
     </row>
-    <row r="33" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -4936,7 +4952,7 @@
         <v>- [Python-装饰器的灵活实现：带参数与不带参数](/Python基础库/20260204-Python-装饰器的灵活实现：带参数与不带参数.md)</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -4949,7 +4965,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -4962,7 +4978,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -4975,7 +4991,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -4988,7 +5004,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -5001,7 +5017,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -5022,17 +5038,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="44.77734375" customWidth="1"/>
-    <col min="3" max="3" width="56.21875" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="44.765625" customWidth="1"/>
+    <col min="3" max="3" width="56.23046875" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5046,7 +5062,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -5062,7 +5078,7 @@
         <v>- [对比Excel，利用pandas进行数据分析各种用法](/Python数据处理/对比Excel，利用pandas进行数据分析各种用法.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -5078,7 +5094,7 @@
         <v>- [对csv文件，又get了新的认知](/Python数据处理/对csv文件，又get了新的认知.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -5094,7 +5110,7 @@
         <v>- [对csv文件，又get了新的认知（二）](/Python数据处理/对csv文件，又get了新的认知（二）.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -5110,7 +5126,7 @@
         <v>- [历史双色球数据分析---python](/Python数据处理/历史双色球数据分析---python.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -5126,7 +5142,7 @@
         <v>- [利用Python计算两个地理位置之间的中点](/Python数据处理/利用Python计算两个地理位置之间的中点.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -5142,7 +5158,7 @@
         <v>- [利用Python模拟Excel数据透视表具有“值显示方式”功能](/Python数据处理/利用Python模拟Excel数据透视表具有“值显示方式”功能.md)</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -5158,7 +5174,7 @@
         <v>- [像excel透视表一样使用pandas透视函数](/Python数据处理/像excel透视表一样使用pandas透视函数.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -5174,7 +5190,7 @@
         <v>- [Numpy中的shuffle和permutation区别](/Python数据处理/Numpy中的shuffle和permutation区别.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -5190,7 +5206,7 @@
         <v>- [pandas-错误提醒：FutureWarning--elementwise-comparison-failed;](/Python数据处理/pandas-错误提醒：FutureWarning--elementwise-comparison-failed;.md)</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -5206,7 +5222,7 @@
         <v>- [Pandas数据处理误区要知其然知其所以然](/Python数据处理/Pandas数据处理误区要知其然知其所以然.md)</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -5222,7 +5238,7 @@
         <v>- [Python--Numpy中的范数](/Python数据处理/Python--Numpy中的范数.md)</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -5238,7 +5254,7 @@
         <v>- [Python-把csv文件转换为excel文件](/Python数据处理/Python-把csv文件转换为excel文件.md)</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -5254,7 +5270,7 @@
         <v>- [Python-常用的加解密算法实例应用](/Python数据处理/Python-常用的加解密算法实例应用.md)</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -5270,7 +5286,7 @@
         <v>- [Python-处理Excel文件为了通用原则，建议用openpyxl库](/Python数据处理/Python-处理Excel文件为了通用原则，建议用openpyxl库.md)</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -5286,7 +5302,7 @@
         <v>- [Python-多线程，真实使用代码](/Python数据处理/Python-多线程，真实使用代码.md)</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -5302,7 +5318,7 @@
         <v>- [Python-基于datetime库的日期时间数据处理](/Python数据处理/Python-基于datetime库的日期时间数据处理.md)</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -5318,7 +5334,7 @@
         <v>- [Python-利用aiohttp异步流式下载文件](/Python数据处理/Python-利用aiohttp异步流式下载文件.md)</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -5334,7 +5350,7 @@
         <v>- [Python-利用Pandas把数据直接导入Mysql](/Python数据处理/Python-利用Pandas把数据直接导入Mysql.md)</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -5350,7 +5366,7 @@
         <v>- [Python-利用pandas对数据进行特定排序](/Python数据处理/Python-利用pandas对数据进行特定排序.md)</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -5366,7 +5382,7 @@
         <v>- [Python-两个字典如何实现相加？（相同的键，值相加）](/Python数据处理/Python-两个字典如何实现相加？（相同的键，值相加）.md)</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -5382,7 +5398,7 @@
         <v>- [Python-小知识系列（一）](/Python数据处理/Python-小知识系列（一）.md)</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -5398,7 +5414,7 @@
         <v>- [Python-字符串格式化方法总结](/Python数据处理/Python-字符串格式化方法总结.md)</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -5414,7 +5430,7 @@
         <v>- [Python-jupyter-常用语句汇总](/Python数据处理/Python-jupyter-常用语句汇总.md)</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -5430,7 +5446,7 @@
         <v>- [Python-pandas-2-0-初探](/Python数据处理/Python-pandas-2-0-初探.md)</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -5446,7 +5462,7 @@
         <v>- [Python-pandas-里面的数据类型坑，astype要慎用](/Python数据处理/Python-pandas-里面的数据类型坑，astype要慎用.md)</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -5462,7 +5478,7 @@
         <v>- [Python-pandas-数据筛选与赋值升级版详解](/Python数据处理/Python-pandas-数据筛选与赋值升级版详解.md)</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -5478,7 +5494,7 @@
         <v>- [Python-pandas-数据无法正常分列](/Python数据处理/Python-pandas-数据无法正常分列.md)</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -5494,7 +5510,7 @@
         <v>- [Python-pandas-str-replace-不起作用](/Python数据处理/Python-pandas-str-replace-不起作用.md)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -5510,7 +5526,7 @@
         <v>- [Python-pandas遍历行数据的2种方法](/Python数据处理/Python-pandas遍历行数据的2种方法.md)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -5526,7 +5542,7 @@
         <v>- [Python-pandas数据分列，分割符号&amp;固定宽度](/Python数据处理/Python-pandas数据分列，分割符号&amp;固定宽度.md)</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -5542,7 +5558,7 @@
         <v>- [Python-pandas数据计数函数value_counts](/Python数据处理/Python-pandas数据计数函数value_counts.md)</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -5558,7 +5574,7 @@
         <v>- [Python-pandas在读取csv文件时（linux与windows之间传输），数据行数不一致的问题](/Python数据处理/Python-pandas在读取csv文件时（linux与windows之间传输），数据行数不一致的问题.md)</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -5574,7 +5590,7 @@
         <v>- [Python常用语句汇总](/Python数据处理/Python常用语句汇总.md)</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -5590,7 +5606,7 @@
         <v>- [Python加载txt数据乱码问题升级版解决方法](/Python数据处理/Python加载txt数据乱码问题升级版解决方法.md)</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -5606,7 +5622,7 @@
         <v>- [Python数据处理中-pd-concat-与-pd-merge-区别](/Python数据处理/Python数据处理中-pd-concat-与-pd-merge-区别.md)</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -5622,7 +5638,7 @@
         <v>- [Python数据预处理中One-Hot编码的方法](/Python数据处理/Python数据预处理中One-Hot编码的方法.md)</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -5638,7 +5654,7 @@
         <v>- [Python通过修改系统注册表，强制设置Excel宏信任级别](/Python数据处理/Python通过修改系统注册表，强制设置Excel宏信任级别.md)</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -5654,7 +5670,7 @@
         <v>- [Python用xlwings库处理Excel](/Python数据处理/Python用xlwings库处理Excel.md)</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -5670,7 +5686,7 @@
         <v>- [Python中的Lambda匿名函数](/Python数据处理/Python中的Lambda匿名函数.md)</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -5686,7 +5702,7 @@
         <v>- [Pythonner还在为了练习Numpy而没有真实数据而烦恼吗？](/Python数据处理/Pythonner还在为了练习Numpy而没有真实数据而烦恼吗？.md)</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -5702,7 +5718,7 @@
         <v>- [Python-pandas中重排列与列重名](/Python数据处理/Python-pandas中重排列与列重名.md)</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -5718,7 +5734,7 @@
         <v>- [Python-Pandas导出Excel时保留URL为纯文本的完美方案](/Python数据处理/Python-Pandas导出Excel时保留URL为纯文本的完美方案.md)</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -5734,7 +5750,7 @@
         <v>- [Python-基于hdfs路径统计hive表存储信息](/Python数据处理/Python-基于hdfs路径统计hive表存储信息.md)</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -5750,7 +5766,7 @@
         <v>- [Python-基于OpenList接口下载夸克网盘资源](/Python数据处理/Python-基于OpenList接口下载夸克网盘资源.md)</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -5766,7 +5782,7 @@
         <v>- [Python-基于pyhive库操作hive](/Python数据处理/Python-基于pyhive库操作hive.md)</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -5782,7 +5798,7 @@
         <v>- [Python-小知识系列-2](/Python数据处理/Python-小知识系列-2.md)</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>38</v>
       </c>
@@ -5795,7 +5811,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>38</v>
       </c>
@@ -5808,7 +5824,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>38</v>
       </c>
@@ -5821,7 +5837,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>38</v>
       </c>
@@ -5834,7 +5850,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>38</v>
       </c>
@@ -5847,7 +5863,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>38</v>
       </c>
@@ -5860,7 +5876,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>38</v>
       </c>
@@ -5873,7 +5889,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>38</v>
       </c>
@@ -5886,7 +5902,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>38</v>
       </c>
@@ -5899,7 +5915,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>38</v>
       </c>
@@ -5912,7 +5928,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>38</v>
       </c>
@@ -5925,7 +5941,7 @@
         <v>- [](/Python数据处理/)</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -5933,6 +5949,105 @@
       <c r="D59" t="str">
         <f t="shared" si="1"/>
         <v>- [](//)</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s">
+        <v>175</v>
+      </c>
+      <c r="C63" t="str">
+        <f>"- ["&amp;MID(B63,10,LEN(B63)-12)&amp;"]("&amp;A63&amp;"/"&amp;B63&amp;")"</f>
+        <v>- [现代Python全栈分布式数据计算：Ray、Daft与Lance的探索](Python数据处理/20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md)</v>
+      </c>
+      <c r="D63" t="str">
+        <f>"- ["&amp;MID(B63,10,LEN(B63)-12)&amp;"](/"&amp;A63&amp;"/"&amp;B63&amp;")"</f>
+        <v>- [现代Python全栈分布式数据计算：Ray、Daft与Lance的探索](/Python数据处理/20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md)</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" t="e">
+        <f t="shared" ref="C64:C69" si="2">"- ["&amp;MID(B64,10,LEN(B64)-12)&amp;"]("&amp;A64&amp;"/"&amp;B64&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D64" t="e">
+        <f t="shared" ref="D64:D69" si="3">"- ["&amp;MID(B64,10,LEN(B64)-12)&amp;"](/"&amp;A64&amp;"/"&amp;B64&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D65" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D66" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D67" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D68" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D69" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -5942,16 +6057,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="24.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5962,7 +6077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -5974,7 +6089,7 @@
         <v>- [利用Python-自己动手制作动漫效果图片](Python图像处理/利用Python-自己动手制作动漫效果图片.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -5986,7 +6101,7 @@
         <v>- [利用Python对图片进行马赛克处理](Python图像处理/利用Python对图片进行马赛克处理.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -5998,7 +6113,7 @@
         <v>- [利用Python对图片进行模糊化处理](Python图像处理/利用Python对图片进行模糊化处理.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -6010,7 +6125,7 @@
         <v>- [Python---opencv一次读取视频里面多张视频帧](Python图像处理/Python---opencv一次读取视频里面多张视频帧.md)</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -6022,7 +6137,7 @@
         <v>- [Python-人脸检测方法总结](Python图像处理/Python-人脸检测方法总结.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -6034,7 +6149,7 @@
         <v>- [Python基于opencv-“三维”旋转图片，解决日常小问题](Python图像处理/Python基于opencv-“三维”旋转图片，解决日常小问题.md)</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -6046,7 +6161,7 @@
         <v>- [Python-利用4行代码实现图片灰度化](Python图像处理/Python-利用4行代码实现图片灰度化.md)</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -6058,7 +6173,7 @@
         <v>- [Python-利用聚类算法对图片进行颜色压缩](Python图像处理/Python-利用聚类算法对图片进行颜色压缩.md)</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -6070,7 +6185,7 @@
         <v>- [Python-微信头像添加国旗](Python图像处理/Python-微信头像添加国旗.md)</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -6082,7 +6197,7 @@
         <v>- [Python-一个在本地给图片添加水印的小工具](Python图像处理/Python-一个在本地给图片添加水印的小工具.md)</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -6094,7 +6209,7 @@
         <v>- [利用Python生成手绘效果的图片](Python图像处理/利用Python生成手绘效果的图片.md)</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -6103,7 +6218,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>79</v>
       </c>
@@ -6115,7 +6230,7 @@
         <v>- [利用Python实现二维码自由](Python图像处理/利用Python实现二维码自由.md)</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -6124,7 +6239,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -6133,7 +6248,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -6142,7 +6257,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>79</v>
       </c>
@@ -6151,7 +6266,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -6160,7 +6275,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -6169,7 +6284,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -6178,7 +6293,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -6187,7 +6302,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -6196,7 +6311,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -6205,7 +6320,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -6214,7 +6329,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -6223,7 +6338,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -6232,7 +6347,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -6241,7 +6356,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -6250,7 +6365,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -6259,7 +6374,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -6268,7 +6383,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -6277,7 +6392,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -6286,7 +6401,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -6295,7 +6410,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -6304,7 +6419,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>79</v>
       </c>
@@ -6313,7 +6428,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -6322,7 +6437,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -6331,7 +6446,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -6340,7 +6455,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -6349,7 +6464,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -6365,17 +6480,17 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.5546875" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
-    <col min="4" max="4" width="96.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.69140625" customWidth="1"/>
+    <col min="2" max="2" width="45.53515625" customWidth="1"/>
+    <col min="3" max="3" width="24.4609375" customWidth="1"/>
+    <col min="4" max="4" width="96.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6389,7 +6504,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -6405,7 +6520,7 @@
         <v>- [Python-利用协程采集想看的《人世间》下载地址](/数据采集/Python-利用协程采集想看的《人世间》下载地址.md)</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -6421,7 +6536,7 @@
         <v>- [Python-中一个好用的股票开源库akshare](/数据采集/Python-中一个好用的股票开源库akshare.md)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -6437,7 +6552,7 @@
         <v>- [Python-利用协程整合IPTV直播源](/数据采集/Python-利用协程整合IPTV直播源.md)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -6450,7 +6565,7 @@
         <v>- [](/数据采集/)</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -6459,7 +6574,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>86</v>
       </c>
@@ -6468,7 +6583,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -6477,7 +6592,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -6486,7 +6601,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -6495,7 +6610,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -6504,7 +6619,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -6513,7 +6628,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>86</v>
       </c>
@@ -6522,7 +6637,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -6531,7 +6646,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -6540,7 +6655,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -6549,7 +6664,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -6558,7 +6673,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -6567,7 +6682,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -6576,7 +6691,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -6585,7 +6700,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -6594,7 +6709,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -6603,7 +6718,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -6612,7 +6727,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>86</v>
       </c>
@@ -6621,7 +6736,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -6630,7 +6745,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>86</v>
       </c>
@@ -6639,7 +6754,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -6648,7 +6763,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>86</v>
       </c>
@@ -6657,7 +6772,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -6666,7 +6781,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -6675,7 +6790,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -6684,7 +6799,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>86</v>
       </c>
@@ -6693,7 +6808,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>86</v>
       </c>
@@ -6702,7 +6817,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -6711,7 +6826,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -6720,7 +6835,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -6729,7 +6844,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>86</v>
       </c>
@@ -6738,7 +6853,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -6747,7 +6862,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -6756,7 +6871,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -6765,7 +6880,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>86</v>
       </c>

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D42214B-CD98-4D9D-85F4-0A42E35A8B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBB9567-D5EB-41CD-B1C6-29FDC83A8F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="177">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -668,6 +668,10 @@
   </si>
   <si>
     <t>20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260313-OpenClaw使用体验.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3578,15 +3582,16 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.69140625" customWidth="1"/>
-    <col min="2" max="2" width="44.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.61328125" customWidth="1"/>
+    <col min="2" max="2" width="36.23046875" customWidth="1"/>
+    <col min="3" max="3" width="37.3828125" customWidth="1"/>
+    <col min="4" max="4" width="22.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3596,8 +3601,11 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D1" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>152</v>
       </c>
@@ -3608,17 +3616,28 @@
         <f>"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"]("&amp;A2&amp;"/"&amp;B2&amp;")"</f>
         <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D2" t="str">
+        <f>"- ["&amp;SUBSTITUTE(B2,".md","")&amp;"](/"&amp;A2&amp;"/"&amp;B2&amp;")"</f>
+        <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](/大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>152</v>
       </c>
-      <c r="C3" t="e">
-        <f t="shared" ref="C3:C16" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C5" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <v>- [基于DeepSeek，构建个人本地RAG知识库](大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D5" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <v>- [基于DeepSeek，构建个人本地RAG知识库](/大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -3626,8 +3645,12 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D4" t="str">
+        <f t="shared" si="1"/>
+        <v>- [](/大模型相关/)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -3635,103 +3658,107 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>- [](/大模型相关/)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>152</v>
       </c>
-      <c r="C8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" t="str">
+        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"]("&amp;A8&amp;"/"&amp;B8&amp;")"</f>
+        <v>- [OpenClaw使用体验](大模型相关/20260313-OpenClaw使用体验.md)</v>
+      </c>
+      <c r="D8" t="str">
+        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"](/"&amp;A8&amp;"/"&amp;B8&amp;")"</f>
+        <v>- [OpenClaw使用体验](/大模型相关/20260313-OpenClaw使用体验.md)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>152</v>
       </c>
       <c r="C9" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" ref="C9:C14" si="2">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" t="e">
+        <f t="shared" ref="D9:D14" si="3">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>152</v>
       </c>
       <c r="C10" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D10" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>152</v>
       </c>
       <c r="C11" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>152</v>
       </c>
       <c r="C12" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>152</v>
       </c>
       <c r="C13" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>152</v>
       </c>
       <c r="C14" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBB9567-D5EB-41CD-B1C6-29FDC83A8F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D3BAFB-9F5D-4339-8810-4D1E20E57EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="916" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,8 @@
     <sheet name="数学知识" sheetId="13" r:id="rId12"/>
     <sheet name="随笔" sheetId="14" r:id="rId13"/>
     <sheet name="clickehouse" sheetId="15" r:id="rId14"/>
-    <sheet name="Web" sheetId="16" r:id="rId15"/>
-    <sheet name="大模型相关" sheetId="17" r:id="rId16"/>
+    <sheet name="大模型相关" sheetId="17" r:id="rId15"/>
+    <sheet name="Web" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="178">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -672,6 +672,10 @@
   </si>
   <si>
     <t>20260313-OpenClaw使用体验.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3392,6 +3396,197 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.61328125" customWidth="1"/>
+    <col min="2" max="2" width="36.23046875" customWidth="1"/>
+    <col min="3" max="3" width="37.3828125" customWidth="1"/>
+    <col min="4" max="4" width="22.23046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" t="str">
+        <f>"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"]("&amp;A2&amp;"/"&amp;B2&amp;")"</f>
+        <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
+      </c>
+      <c r="D2" t="str">
+        <f>"- ["&amp;SUBSTITUTE(B2,".md","")&amp;"](/"&amp;A2&amp;"/"&amp;B2&amp;")"</f>
+        <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](/大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C5" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <v>- [基于DeepSeek，构建个人本地RAG知识库](大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D5" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <v>- [基于DeepSeek，构建个人本地RAG知识库](/大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="1"/>
+        <v>- [](/大模型相关/)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>- [](/大模型相关/)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" t="str">
+        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"]("&amp;A8&amp;"/"&amp;B8&amp;")"</f>
+        <v>- [OpenClaw使用体验](大模型相关/20260313-OpenClaw使用体验.md)</v>
+      </c>
+      <c r="D8" t="str">
+        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"](/"&amp;A8&amp;"/"&amp;B8&amp;")"</f>
+        <v>- [OpenClaw使用体验](/大模型相关/20260313-OpenClaw使用体验.md)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" ref="C9:C14" si="2">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>- [VibeCoding完全指南：2026年，我们用“感觉”写代码](大模型相关/20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码.md)</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" ref="D9:D14" si="3">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>- [VibeCoding完全指南：2026年，我们用“感觉”写代码](/大模型相关/20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码.md)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D10" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -3571,194 +3766,6 @@
       </c>
       <c r="C16" t="e">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="11.61328125" customWidth="1"/>
-    <col min="2" max="2" width="36.23046875" customWidth="1"/>
-    <col min="3" max="3" width="37.3828125" customWidth="1"/>
-    <col min="4" max="4" width="22.23046875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" t="str">
-        <f>"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"]("&amp;A2&amp;"/"&amp;B2&amp;")"</f>
-        <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
-      </c>
-      <c r="D2" t="str">
-        <f>"- ["&amp;SUBSTITUTE(B2,".md","")&amp;"](/"&amp;A2&amp;"/"&amp;B2&amp;")"</f>
-        <v>- [尝试-gemini-cli，在本地开发俄罗斯方块](/大模型相关/尝试-gemini-cli，在本地开发俄罗斯方块.md)</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" ref="C3:C5" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
-        <v>- [基于DeepSeek，构建个人本地RAG知识库](大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" ref="D3:D5" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
-        <v>- [基于DeepSeek，构建个人本地RAG知识库](/大模型相关/基于DeepSeek，构建个人本地RAG知识库.md)</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/大模型相关/)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/大模型相关/)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" t="str">
-        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"]("&amp;A8&amp;"/"&amp;B8&amp;")"</f>
-        <v>- [OpenClaw使用体验](大模型相关/20260313-OpenClaw使用体验.md)</v>
-      </c>
-      <c r="D8" t="str">
-        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"](/"&amp;A8&amp;"/"&amp;B8&amp;")"</f>
-        <v>- [OpenClaw使用体验](/大模型相关/20260313-OpenClaw使用体验.md)</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" t="e">
-        <f t="shared" ref="C9:C14" si="2">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D9" t="e">
-        <f t="shared" ref="D9:D14" si="3">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D10" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D11" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D12" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D13" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D14" t="e">
-        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D3BAFB-9F5D-4339-8810-4D1E20E57EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DB0F29-D622-4B44-8B29-6A73016ED447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="916" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="179">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -676,6 +676,10 @@
   </si>
   <si>
     <t>20260320-VibeCoding完全指南：2026年，我们用“感觉”写代码.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3519,13 +3523,16 @@
       <c r="A10" t="s">
         <v>152</v>
       </c>
-      <c r="C10" t="e">
+      <c r="B10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" t="str">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D10" t="e">
+        <v>- [Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序](大模型相关/20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序.md)</v>
+      </c>
+      <c r="D10" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>- [Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序](/大模型相关/20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序.md)</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DB0F29-D622-4B44-8B29-6A73016ED447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC00EDDF-D534-4C0E-8382-A48B6D84D475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="916" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="180">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -680,6 +680,10 @@
   </si>
   <si>
     <t>20260326-Vibe_Coding初体验：用AI辅助开发一款心情打卡小程序.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260410-Python与Rust类型参数对比：从TypeVar到泛型T.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4997,13 +5001,16 @@
       <c r="A35" t="s">
         <v>25</v>
       </c>
-      <c r="C35" t="e">
+      <c r="B35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" t="str">
         <f t="shared" ref="C35:C40" si="2">"- ["&amp;MID(B35,10,LEN(B35)-12)&amp;"]("&amp;A35&amp;"/"&amp;B35&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D35" t="e">
+        <v>- [Python与Rust类型参数对比：从TypeVar到泛型T](Python基础库/20260410-Python与Rust类型参数对比：从TypeVar到泛型T.md)</v>
+      </c>
+      <c r="D35" t="str">
         <f t="shared" ref="D35:D40" si="3">"- ["&amp;MID(B35,10,LEN(B35)-12)&amp;"](/"&amp;A35&amp;"/"&amp;B35&amp;")"</f>
-        <v>#VALUE!</v>
+        <v>- [Python与Rust类型参数对比：从TypeVar到泛型T](/Python基础库/20260410-Python与Rust类型参数对比：从TypeVar到泛型T.md)</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC00EDDF-D534-4C0E-8382-A48B6D84D475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7CACD8-ECB5-4B4D-B1DA-C77EBDC18CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="916" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="181">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -684,6 +684,10 @@
   </si>
   <si>
     <t>20260410-Python与Rust类型参数对比：从TypeVar到泛型T.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260421-告别焦虑，借助AI深化技术学习.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2730,7 +2734,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.69140625" customWidth="1"/>
@@ -2777,7 +2781,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C41" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="C3:C6" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [吴军老师的《计算之魂》部分重点摘要](随笔/吴军老师的《计算之魂》部分重点摘要.md)</v>
       </c>
       <c r="D3" t="str">
@@ -2830,40 +2834,25 @@
         <v>- [管理的精髓](/随笔/管理的精髓.md)</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>113</v>
       </c>
-      <c r="C10" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="B10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" t="str">
+        <f>"- ["&amp;MID(B10,10,LEN(B10)-12)&amp;"]("&amp;A10&amp;"/"&amp;B10&amp;")"</f>
+        <v>- [告别焦虑，借助AI深化技术学习](随笔/20260421-告别焦虑，借助AI深化技术学习.md)</v>
+      </c>
+      <c r="D10" t="str">
+        <f>"- ["&amp;MID(B10,10,LEN(B10)-12)&amp;"](/"&amp;A10&amp;"/"&amp;B10&amp;")"</f>
+        <v>- [告别焦虑，借助AI深化技术学习](/随笔/20260421-告别焦虑，借助AI深化技术学习.md)</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
@@ -2871,7 +2860,11 @@
         <v>113</v>
       </c>
       <c r="C11" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C11:C16" si="2">"- ["&amp;MID(B11,10,LEN(B11)-12)&amp;"]("&amp;A11&amp;"/"&amp;B11&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" t="e">
+        <f t="shared" ref="D11:D16" si="3">"- ["&amp;MID(B11,10,LEN(B11)-12)&amp;"](/"&amp;A11&amp;"/"&amp;B11&amp;")"</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2880,7 +2873,11 @@
         <v>113</v>
       </c>
       <c r="C12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2889,7 +2886,11 @@
         <v>113</v>
       </c>
       <c r="C13" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2898,7 +2899,11 @@
         <v>113</v>
       </c>
       <c r="C14" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2907,7 +2912,11 @@
         <v>113</v>
       </c>
       <c r="C15" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2916,232 +2925,11 @@
         <v>113</v>
       </c>
       <c r="C16" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D16" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7CACD8-ECB5-4B4D-B1DA-C77EBDC18CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622CBACA-0431-414F-9305-0695C6FE987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="916" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="182">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -689,6 +689,9 @@
   <si>
     <t>20260421-告别焦虑，借助AI深化技术学习.md</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260424-Python异步编程与CPU密集型任务的优雅解法.md</t>
   </si>
 </sst>
 </file>
@@ -3387,7 +3390,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.23046875" bestFit="1" customWidth="1"/>
@@ -3431,11 +3434,11 @@
         <v>146</v>
       </c>
       <c r="C3" t="e">
-        <f t="shared" ref="C3:C16" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="C3:C4" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>#VALUE!</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D6" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="D3:D4" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [](/Web/)</v>
       </c>
     </row>
@@ -3452,48 +3455,25 @@
         <v>- [](/Web/)</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Web/)</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Web/)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>146</v>
       </c>
-      <c r="C8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" t="str">
+        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"]("&amp;A8&amp;"/"&amp;B8&amp;")"</f>
+        <v>- [Python异步编程与CPU密集型任务的优雅解法](Web/20260424-Python异步编程与CPU密集型任务的优雅解法.md)</v>
+      </c>
+      <c r="D8" t="str">
+        <f>"- ["&amp;MID(B8,10,LEN(B8)-12)&amp;"](/"&amp;A8&amp;"/"&amp;B8&amp;")"</f>
+        <v>- [Python异步编程与CPU密集型任务的优雅解法](/Web/20260424-Python异步编程与CPU密集型任务的优雅解法.md)</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
@@ -3501,7 +3481,11 @@
         <v>146</v>
       </c>
       <c r="C9" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C9:C14" si="2">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" t="e">
+        <f t="shared" ref="D9:D14" si="3">"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3510,7 +3494,11 @@
         <v>146</v>
       </c>
       <c r="C10" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D10" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3519,7 +3507,11 @@
         <v>146</v>
       </c>
       <c r="C11" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3528,7 +3520,11 @@
         <v>146</v>
       </c>
       <c r="C12" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3537,7 +3533,11 @@
         <v>146</v>
       </c>
       <c r="C13" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3546,25 +3546,11 @@
         <v>146</v>
       </c>
       <c r="C14" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4271,7 +4257,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.69140625" customWidth="1"/>
-    <col min="2" max="2" width="58.53515625" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="88.53515625" customWidth="1"/>
     <col min="4" max="4" width="23.53515625" customWidth="1"/>
   </cols>

--- a/src/文章列表.xlsx
+++ b/src/文章列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622CBACA-0431-414F-9305-0695C6FE987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E268BA-78D2-464D-A348-EF1EA758232C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="916" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="183">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -692,6 +692,10 @@
   </si>
   <si>
     <t>20260424-Python异步编程与CPU密集型任务的优雅解法.md</t>
+  </si>
+  <si>
+    <t>20260430-Python-本地给图片添加水印的GUI小工具.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4861,7 +4865,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.69140625" customWidth="1"/>
@@ -4908,11 +4912,11 @@
         <v>40</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C59" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="C3:C47" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [对csv文件，又get了新的认知](Python数据处理/对csv文件，又get了新的认知.md)</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D59" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="D3:D47" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [对csv文件，又get了新的认知](/Python数据处理/对csv文件，又get了新的认知.md)</v>
       </c>
     </row>
@@ -5620,56 +5624,25 @@
         <v>- [Python-小知识系列-2](/Python数据处理/Python-小知识系列-2.md)</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D48" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D49" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>38</v>
-      </c>
-      <c r="C50" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D50" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+    <row r="50" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>38</v>
       </c>
-      <c r="C51" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="B51" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" t="str">
+        <f>"- ["&amp;MID(B51,10,LEN(B51)-12)&amp;"]("&amp;A51&amp;"/"&amp;B51&amp;")"</f>
+        <v>- [现代Python全栈分布式数据计算：Ray、Daft与Lance的探索](Python数据处理/20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md)</v>
       </c>
       <c r="D51" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+        <f>"- ["&amp;MID(B51,10,LEN(B51)-12)&amp;"](/"&amp;A51&amp;"/"&amp;B51&amp;")"</f>
+        <v>- [现代Python全栈分布式数据计算：Ray、Daft与Lance的探索](/Python数据处理/20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md)</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
@@ -5677,12 +5650,12 @@
         <v>38</v>
       </c>
       <c r="C52" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D52" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+        <f t="shared" ref="C52:C57" si="2">"- ["&amp;MID(B52,10,LEN(B52)-12)&amp;"]("&amp;A52&amp;"/"&amp;B52&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D52" t="e">
+        <f t="shared" ref="D52:D57" si="3">"- ["&amp;MID(B52,10,LEN(B52)-12)&amp;"](/"&amp;A52&amp;"/"&amp;B52&amp;")"</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
@@ -5690,12 +5663,12 @@
         <v>38</v>
       </c>
       <c r="C53" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D53" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D53" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
@@ -5703,12 +5676,12 @@
         <v>38</v>
       </c>
       <c r="C54" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D54" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D54" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -5716,12 +5689,12 @@
         <v>38</v>
       </c>
       <c r="C55" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D55" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D55" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
@@ -5729,12 +5702,12 @@
         <v>38</v>
       </c>
       <c r="C56" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D56" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D56" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
@@ -5742,132 +5715,10 @@
         <v>38</v>
       </c>
       <c r="C57" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D57" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D58" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](/Python数据处理/)</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C59" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D59" t="str">
-        <f t="shared" si="1"/>
-        <v>- [](//)</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" t="s">
-        <v>175</v>
-      </c>
-      <c r="C63" t="str">
-        <f>"- ["&amp;MID(B63,10,LEN(B63)-12)&amp;"]("&amp;A63&amp;"/"&amp;B63&amp;")"</f>
-        <v>- [现代Python全栈分布式数据计算：Ray、Daft与Lance的探索](Python数据处理/20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md)</v>
-      </c>
-      <c r="D63" t="str">
-        <f>"- ["&amp;MID(B63,10,LEN(B63)-12)&amp;"](/"&amp;A63&amp;"/"&amp;B63&amp;")"</f>
-        <v>- [现代Python全栈分布式数据计算：Ray、Daft与Lance的探索](/Python数据处理/20260228-现代Python全栈分布式数据计算：Ray、Daft与Lance的探索.md)</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>38</v>
-      </c>
-      <c r="C64" t="e">
-        <f t="shared" ref="C64:C69" si="2">"- ["&amp;MID(B64,10,LEN(B64)-12)&amp;"]("&amp;A64&amp;"/"&amp;B64&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D64" t="e">
-        <f t="shared" ref="D64:D69" si="3">"- ["&amp;MID(B64,10,LEN(B64)-12)&amp;"](/"&amp;A64&amp;"/"&amp;B64&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="D65" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>38</v>
-      </c>
-      <c r="C66" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D66" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D67" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>38</v>
-      </c>
-      <c r="C68" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D68" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>38</v>
-      </c>
-      <c r="C69" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D69" t="e">
+      <c r="D57" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
@@ -5880,26 +5731,30 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.69140625" customWidth="1"/>
     <col min="2" max="2" width="45.53515625" customWidth="1"/>
-    <col min="3" max="3" width="24.4609375" customWidth="1"/>
+    <col min="3" max="3" width="32.3046875" customWidth="1"/>
+    <col min="4" max="4" width="42.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D1" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -5910,8 +5765,12 @@
         <f>"- ["&amp;LEFT(B2,LEN(B2)-3)&amp;"]("&amp;A2&amp;"/"&amp;B2&amp;")"</f>
         <v>- [利用Python-自己动手制作动漫效果图片](Python图像处理/利用Python-自己动手制作动漫效果图片.md)</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D2" t="str">
+        <f>"- ["&amp;SUBSTITUTE(B2,".md","")&amp;"](/"&amp;A2&amp;"/"&amp;B2&amp;")"</f>
+        <v>- [利用Python-自己动手制作动漫效果图片](/Python图像处理/利用Python-自己动手制作动漫效果图片.md)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -5919,11 +5778,15 @@
         <v>81</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C41" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="C3:C13" si="0">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [利用Python对图片进行马赛克处理](Python图像处理/利用Python对图片进行马赛克处理.md)</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D13" si="1">"- ["&amp;SUBSTITUTE(B3,".md","")&amp;"](/"&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <v>- [利用Python对图片进行马赛克处理](/Python图像处理/利用Python对图片进行马赛克处理.md)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -5934,8 +5797,12 @@
         <f t="shared" si="0"/>
         <v>- [利用Python对图片进行模糊化处理](Python图像处理/利用Python对图片进行模糊化处理.md)</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D4" t="str">
+        <f t="shared" si="1"/>
+        <v>- [利用Python对图片进行模糊化处理](/Python图像处理/利用Python对图片进行模糊化处理.md)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -5946,8 +5813,12 @@
         <f t="shared" si="0"/>
         <v>- [Python---opencv一次读取视频里面多张视频帧](Python图像处理/Python---opencv一次读取视频里面多张视频帧.md)</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python---opencv一次读取视频里面多张视频帧](/Python图像处理/Python---opencv一次读取视频里面多张视频帧.md)</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -5958,8 +5829,12 @@
         <f t="shared" si="0"/>
         <v>- [Python-人脸检测方法总结](Python图像处理/Python-人脸检测方法总结.md)</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D6" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python-人脸检测方法总结](/Python图像处理/Python-人脸检测方法总结.md)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -5970,8 +5845,12 @@
         <f t="shared" si="0"/>
         <v>- [Python基于opencv-“三维”旋转图片，解决日常小问题](Python图像处理/Python基于opencv-“三维”旋转图片，解决日常小问题.md)</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D7" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python基于opencv-“三维”旋转图片，解决日常小问题](/Python图像处理/Python基于opencv-“三维”旋转图片，解决日常小问题.md)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -5982,8 +5861,12 @@
         <f t="shared" si="0"/>
         <v>- [Python-利用4行代码实现图片灰度化](Python图像处理/Python-利用4行代码实现图片灰度化.md)</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D8" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python-利用4行代码实现图片灰度化](/Python图像处理/Python-利用4行代码实现图片灰度化.md)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -5994,8 +5877,12 @@
         <f t="shared" si="0"/>
         <v>- [Python-利用聚类算法对图片进行颜色压缩](Python图像处理/Python-利用聚类算法对图片进行颜色压缩.md)</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D9" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python-利用聚类算法对图片进行颜色压缩](/Python图像处理/Python-利用聚类算法对图片进行颜色压缩.md)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -6006,8 +5893,12 @@
         <f t="shared" si="0"/>
         <v>- [Python-微信头像添加国旗](Python图像处理/Python-微信头像添加国旗.md)</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D10" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python-微信头像添加国旗](/Python图像处理/Python-微信头像添加国旗.md)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -6018,8 +5909,12 @@
         <f t="shared" si="0"/>
         <v>- [Python-一个在本地给图片添加水印的小工具](Python图像处理/Python-一个在本地给图片添加水印的小工具.md)</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D11" t="str">
+        <f t="shared" si="1"/>
+        <v>- [Python-一个在本地给图片添加水印的小工具](/Python图像处理/Python-一个在本地给图片添加水印的小工具.md)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>79</v>
       </c>
@@ -6030,268 +5925,123 @@
         <f t="shared" si="0"/>
         <v>- [利用Python生成手绘效果的图片](Python图像处理/利用Python生成手绘效果的图片.md)</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D12" t="str">
+        <f t="shared" si="1"/>
+        <v>- [利用Python生成手绘效果的图片](/Python图像处理/利用Python生成手绘效果的图片.md)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>79</v>
       </c>
-      <c r="C13" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B13" t="s">
         <v>155</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C13" t="str">
         <f t="shared" si="0"/>
         <v>- [利用Python实现二维码自由](Python图像处理/利用Python实现二维码自由.md)</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D13" t="str">
+        <f t="shared" si="1"/>
+        <v>- [利用Python实现二维码自由](/Python图像处理/利用Python实现二维码自由.md)</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>79</v>
       </c>
-      <c r="C17" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" t="str">
+        <f>"- ["&amp;MID(B17,10,LEN(B17)-12)&amp;"]("&amp;A17&amp;"/"&amp;B17&amp;")"</f>
+        <v>- [Python-本地给图片添加水印的GUI小工具](Python图像处理/20260430-Python-本地给图片添加水印的GUI小工具.md)</v>
+      </c>
+      <c r="D17" t="str">
+        <f>"- ["&amp;MID(B17,10,LEN(B17)-12)&amp;"](/"&amp;A17&amp;"/"&amp;B17&amp;")"</f>
+        <v>- [Python-本地给图片添加水印的GUI小工具](/Python图像处理/20260430-Python-本地给图片添加水印的GUI小工具.md)</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>79</v>
       </c>
       <c r="C18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" ref="C18:C23" si="2">"- ["&amp;MID(B18,10,LEN(B18)-12)&amp;"]("&amp;A18&amp;"/"&amp;B18&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D18" t="e">
+        <f t="shared" ref="D18:D23" si="3">"- ["&amp;MID(B18,10,LEN(B18)-12)&amp;"](/"&amp;A18&amp;"/"&amp;B18&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>79</v>
       </c>
       <c r="C19" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D19" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>79</v>
       </c>
       <c r="C20" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D20" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>79</v>
       </c>
       <c r="C21" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D21" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>79</v>
       </c>
       <c r="C22" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D22" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>79</v>
       </c>
       <c r="C23" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D23" t="e">
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
